--- a/Listado de adecuaciones curriculares CTP Sabalito 2026 14 mayo 2026.xlsx
+++ b/Listado de adecuaciones curriculares CTP Sabalito 2026 14 mayo 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\REGISTRO_TFG\ANEXO 2\ANEXO_2.git.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E5E5F4-31AE-4F86-8730-6F10EB7136C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CF20D8-FC58-462F-BAF5-9B9EEB26B78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{20044B6B-C64F-41F7-8D7F-0DA7B5245739}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="13740" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{20044B6B-C64F-41F7-8D7F-0DA7B5245739}"/>
   </bookViews>
   <sheets>
     <sheet name="Adecuaciones no significativas" sheetId="2" r:id="rId1"/>
@@ -21,8 +21,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Adecuaciones de Acceso'!$B$6:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Adecuaciones no significativas'!$A$6:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Adecuaciones Significativas'!$A$6:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Adecuaciones no significativas'!$A$6:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Adecuaciones Significativas'!$A$6:$G$44</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2301,6 +2301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF6C38BA-4EDB-4B58-B46A-A5A7847CD75B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
@@ -2369,7 +2370,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15">
+    <row r="8" spans="1:6" ht="15" hidden="1">
       <c r="A8" s="23">
         <v>2</v>
       </c>
@@ -2386,7 +2387,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15">
+    <row r="9" spans="1:6" ht="15" hidden="1">
       <c r="A9" s="23">
         <v>3</v>
       </c>
@@ -2404,7 +2405,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1">
+    <row r="10" spans="1:6" ht="30" hidden="1" customHeight="1">
       <c r="A10" s="23">
         <v>4</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15">
+    <row r="11" spans="1:6" ht="15" hidden="1">
       <c r="A11" s="23">
         <v>5</v>
       </c>
@@ -2439,7 +2440,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15">
+    <row r="12" spans="1:6" ht="15" hidden="1">
       <c r="A12" s="23">
         <v>6</v>
       </c>
@@ -2457,7 +2458,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15">
+    <row r="13" spans="1:6" ht="15" hidden="1">
       <c r="A13" s="23">
         <v>7</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15">
+    <row r="14" spans="1:6" ht="15" hidden="1">
       <c r="A14" s="23">
         <v>8</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15">
+    <row r="15" spans="1:6" ht="15" hidden="1">
       <c r="A15" s="23">
         <v>9</v>
       </c>
@@ -2510,7 +2511,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15">
+    <row r="16" spans="1:6" ht="15" hidden="1">
       <c r="A16" s="23">
         <v>10</v>
       </c>
@@ -2528,7 +2529,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15">
+    <row r="17" spans="1:6" ht="15" hidden="1">
       <c r="A17" s="23">
         <v>11</v>
       </c>
@@ -2546,7 +2547,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15">
+    <row r="18" spans="1:6" ht="15" hidden="1">
       <c r="A18" s="23">
         <v>12</v>
       </c>
@@ -2564,7 +2565,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15">
+    <row r="19" spans="1:6" ht="15" hidden="1">
       <c r="A19" s="23">
         <v>13</v>
       </c>
@@ -2580,7 +2581,7 @@
       <c r="E19" s="24"/>
       <c r="F19" s="65"/>
     </row>
-    <row r="20" spans="1:6" ht="30">
+    <row r="20" spans="1:6" ht="30" hidden="1">
       <c r="A20" s="23">
         <v>14</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15">
+    <row r="21" spans="1:6" ht="15" hidden="1">
       <c r="A21" s="23">
         <v>15</v>
       </c>
@@ -2616,7 +2617,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15">
+    <row r="22" spans="1:6" ht="15" hidden="1">
       <c r="A22" s="23">
         <v>16</v>
       </c>
@@ -2634,7 +2635,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15">
+    <row r="23" spans="1:6" ht="15" hidden="1">
       <c r="A23" s="23">
         <v>17</v>
       </c>
@@ -2654,7 +2655,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15">
+    <row r="24" spans="1:6" ht="15" hidden="1">
       <c r="A24" s="23">
         <v>18</v>
       </c>
@@ -2671,7 +2672,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15">
+    <row r="25" spans="1:6" ht="15" hidden="1">
       <c r="A25" s="23">
         <v>19</v>
       </c>
@@ -2708,7 +2709,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15">
+    <row r="27" spans="1:6" ht="15" hidden="1">
       <c r="A27" s="23">
         <v>21</v>
       </c>
@@ -2726,7 +2727,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15">
+    <row r="28" spans="1:6" ht="15" hidden="1">
       <c r="A28" s="23">
         <v>22</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1">
+    <row r="29" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A29" s="23">
         <v>23</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+    <row r="31" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A31" s="23">
         <v>25</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15">
+    <row r="32" spans="1:6" ht="15" hidden="1">
       <c r="A32" s="23">
         <v>26</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1">
+    <row r="33" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A33" s="23">
         <v>27</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+    <row r="34" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A34" s="23">
         <v>28</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15">
+    <row r="35" spans="1:6" ht="15" hidden="1">
       <c r="A35" s="23">
         <v>29</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15">
+    <row r="36" spans="1:6" ht="15" hidden="1">
       <c r="A36" s="23">
         <v>30</v>
       </c>
@@ -2888,7 +2889,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15">
+    <row r="37" spans="1:6" ht="15" hidden="1">
       <c r="A37" s="23">
         <v>31</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1">
+    <row r="38" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A38" s="23">
         <v>32</v>
       </c>
@@ -2941,7 +2942,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1">
+    <row r="40" spans="1:6" ht="15" hidden="1" customHeight="1">
       <c r="A40" s="23">
         <v>34</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+    <row r="41" spans="1:6" ht="15.75" hidden="1" customHeight="1">
       <c r="A41" s="23">
         <v>35</v>
       </c>
@@ -2975,7 +2976,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15">
+    <row r="42" spans="1:6" ht="15" hidden="1">
       <c r="A42" s="23">
         <v>36</v>
       </c>
@@ -2993,7 +2994,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15">
+    <row r="43" spans="1:6" ht="15" hidden="1">
       <c r="A43" s="23">
         <v>37</v>
       </c>
@@ -3011,7 +3012,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15">
+    <row r="44" spans="1:6" ht="15" hidden="1">
       <c r="A44" s="23">
         <v>38</v>
       </c>
@@ -3046,7 +3047,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15">
+    <row r="46" spans="1:6" ht="15" hidden="1">
       <c r="A46" s="23">
         <v>40</v>
       </c>
@@ -3064,7 +3065,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15">
+    <row r="47" spans="1:6" ht="15" hidden="1">
       <c r="A47" s="23">
         <v>41</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15">
+    <row r="48" spans="1:6" ht="15" hidden="1">
       <c r="A48" s="23">
         <v>42</v>
       </c>
@@ -3099,7 +3100,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15">
+    <row r="49" spans="1:9" ht="15" hidden="1">
       <c r="A49" s="23">
         <v>43</v>
       </c>
@@ -3116,7 +3117,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15">
+    <row r="50" spans="1:9" ht="15" hidden="1">
       <c r="A50" s="23">
         <v>44</v>
       </c>
@@ -3134,7 +3135,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15">
+    <row r="51" spans="1:9" ht="15" hidden="1">
       <c r="A51" s="23">
         <v>45</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15">
+    <row r="52" spans="1:9" ht="15" hidden="1">
       <c r="A52" s="23">
         <v>46</v>
       </c>
@@ -3168,7 +3169,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15">
+    <row r="53" spans="1:9" ht="15" hidden="1">
       <c r="A53" s="23">
         <v>47</v>
       </c>
@@ -3186,7 +3187,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15">
+    <row r="54" spans="1:9" ht="15" hidden="1">
       <c r="A54" s="23">
         <v>48</v>
       </c>
@@ -3204,7 +3205,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15">
+    <row r="55" spans="1:9" ht="15" hidden="1">
       <c r="A55" s="23">
         <v>49</v>
       </c>
@@ -3222,7 +3223,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15">
+    <row r="56" spans="1:9" ht="15" hidden="1">
       <c r="A56" s="23">
         <v>50</v>
       </c>
@@ -3240,7 +3241,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15">
+    <row r="57" spans="1:9" ht="15" hidden="1">
       <c r="A57" s="23">
         <v>51</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="66.75" customHeight="1">
+    <row r="58" spans="1:9" ht="66.75" hidden="1" customHeight="1">
       <c r="A58" s="23">
         <v>52</v>
       </c>
@@ -3273,7 +3274,7 @@
       <c r="E58" s="25"/>
       <c r="F58" s="65"/>
     </row>
-    <row r="59" spans="1:9" ht="15" customHeight="1">
+    <row r="59" spans="1:9" ht="15" hidden="1" customHeight="1">
       <c r="A59" s="23">
         <v>53</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.25" customHeight="1">
+    <row r="60" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A60" s="23">
         <v>54</v>
       </c>
@@ -3310,7 +3311,7 @@
       <c r="H60" s="54"/>
       <c r="I60" s="55"/>
     </row>
-    <row r="61" spans="1:9" ht="14.25" customHeight="1">
+    <row r="61" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A61" s="23">
         <v>55</v>
       </c>
@@ -3333,7 +3334,7 @@
       <c r="H61" s="54"/>
       <c r="I61" s="55"/>
     </row>
-    <row r="62" spans="1:9" ht="14.25" customHeight="1">
+    <row r="62" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A62" s="23">
         <v>56</v>
       </c>
@@ -3353,7 +3354,7 @@
       <c r="H62" s="54"/>
       <c r="I62" s="55"/>
     </row>
-    <row r="63" spans="1:9" ht="14.25" customHeight="1">
+    <row r="63" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A63" s="23">
         <v>57</v>
       </c>
@@ -3373,7 +3374,7 @@
       <c r="H63" s="54"/>
       <c r="I63" s="55"/>
     </row>
-    <row r="64" spans="1:9" ht="14.25" customHeight="1">
+    <row r="64" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A64" s="23">
         <v>58</v>
       </c>
@@ -3393,7 +3394,7 @@
       <c r="H64" s="54"/>
       <c r="I64" s="55"/>
     </row>
-    <row r="65" spans="1:9" ht="14.25" customHeight="1">
+    <row r="65" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A65" s="23">
         <v>59</v>
       </c>
@@ -3413,7 +3414,7 @@
       <c r="H65" s="54"/>
       <c r="I65" s="55"/>
     </row>
-    <row r="66" spans="1:9" ht="14.25" customHeight="1">
+    <row r="66" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A66" s="23">
         <v>60</v>
       </c>
@@ -3434,7 +3435,7 @@
       <c r="H66" s="54"/>
       <c r="I66" s="55"/>
     </row>
-    <row r="67" spans="1:9" ht="14.25" customHeight="1">
+    <row r="67" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A67" s="23">
         <v>61</v>
       </c>
@@ -3454,7 +3455,7 @@
       <c r="H67" s="54"/>
       <c r="I67" s="55"/>
     </row>
-    <row r="68" spans="1:9" ht="14.25" customHeight="1">
+    <row r="68" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A68" s="23">
         <v>62</v>
       </c>
@@ -3474,7 +3475,7 @@
       <c r="H68" s="54"/>
       <c r="I68" s="55"/>
     </row>
-    <row r="69" spans="1:9" ht="14.25" customHeight="1">
+    <row r="69" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A69" s="23">
         <v>63</v>
       </c>
@@ -3495,7 +3496,7 @@
       <c r="H69" s="54"/>
       <c r="I69" s="55"/>
     </row>
-    <row r="70" spans="1:9" ht="14.25" customHeight="1">
+    <row r="70" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A70" s="23">
         <v>64</v>
       </c>
@@ -3536,7 +3537,7 @@
       <c r="H71" s="54"/>
       <c r="I71" s="55"/>
     </row>
-    <row r="72" spans="1:9" ht="14.25" customHeight="1">
+    <row r="72" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A72" s="23">
         <v>66</v>
       </c>
@@ -3557,7 +3558,7 @@
       <c r="H72" s="54"/>
       <c r="I72" s="55"/>
     </row>
-    <row r="73" spans="1:9" ht="14.25" customHeight="1">
+    <row r="73" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A73" s="23">
         <v>67</v>
       </c>
@@ -3578,7 +3579,7 @@
       <c r="H73" s="54"/>
       <c r="I73" s="55"/>
     </row>
-    <row r="74" spans="1:9" ht="14.25" customHeight="1">
+    <row r="74" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A74" s="23">
         <v>67</v>
       </c>
@@ -3599,7 +3600,7 @@
       <c r="H74" s="54"/>
       <c r="I74" s="55"/>
     </row>
-    <row r="75" spans="1:9" ht="14.25" customHeight="1">
+    <row r="75" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A75" s="23">
         <v>69</v>
       </c>
@@ -3619,7 +3620,7 @@
       <c r="H75" s="54"/>
       <c r="I75" s="55"/>
     </row>
-    <row r="76" spans="1:9" ht="14.25" customHeight="1">
+    <row r="76" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A76" s="23">
         <v>70</v>
       </c>
@@ -3640,7 +3641,7 @@
       <c r="H76" s="54"/>
       <c r="I76" s="55"/>
     </row>
-    <row r="77" spans="1:9" ht="14.25" customHeight="1">
+    <row r="77" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A77" s="23">
         <v>71</v>
       </c>
@@ -3660,7 +3661,7 @@
       <c r="H77" s="54"/>
       <c r="I77" s="55"/>
     </row>
-    <row r="78" spans="1:9" ht="14.25" customHeight="1">
+    <row r="78" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A78" s="23">
         <v>72</v>
       </c>
@@ -3681,7 +3682,7 @@
       <c r="H78" s="54"/>
       <c r="I78" s="55"/>
     </row>
-    <row r="79" spans="1:9" ht="14.25" customHeight="1">
+    <row r="79" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A79" s="23">
         <v>73</v>
       </c>
@@ -3701,7 +3702,7 @@
       <c r="H79" s="54"/>
       <c r="I79" s="55"/>
     </row>
-    <row r="80" spans="1:9" ht="14.25" customHeight="1">
+    <row r="80" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A80" s="23">
         <v>74</v>
       </c>
@@ -3721,7 +3722,7 @@
       <c r="H80" s="54"/>
       <c r="I80" s="55"/>
     </row>
-    <row r="81" spans="1:9" ht="14.25" customHeight="1">
+    <row r="81" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A81" s="23">
         <v>75</v>
       </c>
@@ -3742,7 +3743,7 @@
       <c r="H81" s="54"/>
       <c r="I81" s="55"/>
     </row>
-    <row r="82" spans="1:9" ht="14.25" customHeight="1">
+    <row r="82" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A82" s="23">
         <v>76</v>
       </c>
@@ -3763,7 +3764,7 @@
       <c r="H82" s="54"/>
       <c r="I82" s="55"/>
     </row>
-    <row r="83" spans="1:9" ht="14.25" customHeight="1">
+    <row r="83" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A83" s="23">
         <v>77</v>
       </c>
@@ -3784,7 +3785,7 @@
       <c r="H83" s="54"/>
       <c r="I83" s="55"/>
     </row>
-    <row r="84" spans="1:9" ht="14.25" customHeight="1">
+    <row r="84" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A84" s="23">
         <v>78</v>
       </c>
@@ -3804,7 +3805,7 @@
       <c r="H84" s="54"/>
       <c r="I84" s="55"/>
     </row>
-    <row r="85" spans="1:9" ht="14.25" customHeight="1">
+    <row r="85" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A85" s="23">
         <v>79</v>
       </c>
@@ -3825,7 +3826,7 @@
       <c r="H85" s="54"/>
       <c r="I85" s="55"/>
     </row>
-    <row r="86" spans="1:9" ht="14.25" customHeight="1">
+    <row r="86" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A86" s="23">
         <v>80</v>
       </c>
@@ -3845,7 +3846,7 @@
       <c r="H86" s="54"/>
       <c r="I86" s="55"/>
     </row>
-    <row r="87" spans="1:9" ht="14.25" customHeight="1">
+    <row r="87" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A87" s="23">
         <v>81</v>
       </c>
@@ -3866,7 +3867,7 @@
       <c r="H87" s="54"/>
       <c r="I87" s="55"/>
     </row>
-    <row r="88" spans="1:9" ht="14.25" customHeight="1">
+    <row r="88" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A88" s="23">
         <v>82</v>
       </c>
@@ -3886,7 +3887,7 @@
       <c r="H88" s="54"/>
       <c r="I88" s="55"/>
     </row>
-    <row r="89" spans="1:9" ht="14.25" customHeight="1">
+    <row r="89" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A89" s="23">
         <v>83</v>
       </c>
@@ -3907,7 +3908,7 @@
       <c r="H89" s="54"/>
       <c r="I89" s="55"/>
     </row>
-    <row r="90" spans="1:9" ht="14.25" customHeight="1">
+    <row r="90" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A90" s="23">
         <v>84</v>
       </c>
@@ -3928,7 +3929,7 @@
       <c r="H90" s="54"/>
       <c r="I90" s="55"/>
     </row>
-    <row r="91" spans="1:9" ht="14.25" customHeight="1">
+    <row r="91" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A91" s="23">
         <v>85</v>
       </c>
@@ -3948,7 +3949,7 @@
       <c r="H91" s="54"/>
       <c r="I91" s="55"/>
     </row>
-    <row r="92" spans="1:9" ht="14.25" customHeight="1">
+    <row r="92" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A92" s="23">
         <v>86</v>
       </c>
@@ -3989,7 +3990,7 @@
       <c r="H93" s="54"/>
       <c r="I93" s="55"/>
     </row>
-    <row r="94" spans="1:9" ht="14.25" customHeight="1">
+    <row r="94" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A94" s="23">
         <v>88</v>
       </c>
@@ -4009,7 +4010,7 @@
       <c r="H94" s="54"/>
       <c r="I94" s="55"/>
     </row>
-    <row r="95" spans="1:9" ht="14.25" customHeight="1">
+    <row r="95" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A95" s="23">
         <v>89</v>
       </c>
@@ -4029,7 +4030,7 @@
       <c r="H95" s="54"/>
       <c r="I95" s="55"/>
     </row>
-    <row r="96" spans="1:9" ht="14.25" customHeight="1">
+    <row r="96" spans="1:9" ht="14.25" hidden="1" customHeight="1">
       <c r="A96" s="23">
         <v>90</v>
       </c>
@@ -4050,7 +4051,7 @@
       <c r="H96" s="54"/>
       <c r="I96" s="55"/>
     </row>
-    <row r="97" spans="1:6" ht="14.25" customHeight="1">
+    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A97" s="23">
         <v>91</v>
       </c>
@@ -4082,7 +4083,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="14.25" customHeight="1">
+    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A99" s="23">
         <v>93</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="14.25" customHeight="1">
+    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A100" s="23">
         <v>94</v>
       </c>
@@ -4116,7 +4117,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="14.25" customHeight="1">
+    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A101" s="23">
         <v>95</v>
       </c>
@@ -4134,7 +4135,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="14.25" customHeight="1">
+    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A102" s="23">
         <v>96</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="14.25" customHeight="1">
+    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A103" s="23">
         <v>97</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="14.25" customHeight="1">
+    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A104" s="23">
         <v>98</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="14.25" customHeight="1">
+    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A105" s="23">
         <v>99</v>
       </c>
@@ -4206,7 +4207,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="14.25" customHeight="1">
+    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A106" s="23">
         <v>100</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="14.25" customHeight="1">
+    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1">
       <c r="A107" s="23">
         <v>101</v>
       </c>
@@ -4318,7 +4319,12 @@
       <c r="C117" s="97"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:F59" xr:uid="{FF6C38BA-4EDB-4B58-B46A-A5A7847CD75B}">
+  <autoFilter ref="A6:F107" xr:uid="{FF6C38BA-4EDB-4B58-B46A-A5A7847CD75B}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="7-1"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:F96">
       <sortCondition ref="B6:B59"/>
     </sortState>
@@ -4335,6 +4341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478D8F30-1DEF-4E7C-A5F2-B34E61C5B8D1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
@@ -4388,7 +4395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.5">
+    <row r="7" spans="1:8" ht="28.5" hidden="1">
       <c r="A7" s="68">
         <v>1</v>
       </c>
@@ -4411,7 +4418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" s="68">
         <v>2</v>
       </c>
@@ -4434,7 +4441,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" s="68">
         <v>3</v>
       </c>
@@ -4460,7 +4467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5">
+    <row r="10" spans="1:8" ht="28.5" hidden="1">
       <c r="A10" s="68">
         <v>4</v>
       </c>
@@ -4535,7 +4542,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="28.5">
+    <row r="13" spans="1:8" ht="28.5" hidden="1">
       <c r="A13" s="68">
         <v>7</v>
       </c>
@@ -4558,7 +4565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28.5">
+    <row r="14" spans="1:8" ht="28.5" hidden="1">
       <c r="A14" s="68">
         <v>8</v>
       </c>
@@ -4607,7 +4614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" s="68">
         <v>10</v>
       </c>
@@ -4630,7 +4637,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" hidden="1">
       <c r="A17" s="68">
         <v>11</v>
       </c>
@@ -4653,7 +4660,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="28.5">
+    <row r="18" spans="1:8" ht="28.5" hidden="1">
       <c r="A18" s="68">
         <v>12</v>
       </c>
@@ -4676,7 +4683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" s="68">
         <v>13</v>
       </c>
@@ -4699,7 +4706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="28.5">
+    <row r="20" spans="1:8" ht="28.5" hidden="1">
       <c r="A20" s="68">
         <v>14</v>
       </c>
@@ -4722,7 +4729,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.5">
+    <row r="21" spans="1:8" ht="28.5" hidden="1">
       <c r="A21" s="68">
         <v>15</v>
       </c>
@@ -4745,7 +4752,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" hidden="1">
       <c r="A22" s="68">
         <v>16</v>
       </c>
@@ -4768,7 +4775,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="28.5">
+    <row r="23" spans="1:8" ht="28.5" hidden="1">
       <c r="A23" s="68">
         <v>17</v>
       </c>
@@ -4791,7 +4798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="28.5">
+    <row r="24" spans="1:8" ht="28.5" hidden="1">
       <c r="A24" s="68">
         <v>18</v>
       </c>
@@ -4814,7 +4821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" s="68">
         <v>19</v>
       </c>
@@ -4837,7 +4844,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="29.25">
+    <row r="26" spans="1:8" ht="29.25" hidden="1">
       <c r="A26" s="68">
         <v>20</v>
       </c>
@@ -4863,7 +4870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" hidden="1">
       <c r="A27" s="68">
         <v>21</v>
       </c>
@@ -4886,7 +4893,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27" customHeight="1">
+    <row r="28" spans="1:8" ht="27" hidden="1" customHeight="1">
       <c r="A28" s="68">
         <v>22</v>
       </c>
@@ -4930,7 +4937,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" s="68">
         <v>24</v>
       </c>
@@ -4951,7 +4958,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" s="68">
         <v>25</v>
       </c>
@@ -5012,7 +5019,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" s="47">
         <v>28</v>
       </c>
@@ -5033,7 +5040,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" s="47">
         <v>29</v>
       </c>
@@ -5054,7 +5061,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" s="47">
         <v>30</v>
       </c>
@@ -5075,7 +5082,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" s="47">
         <v>31</v>
       </c>
@@ -5117,7 +5124,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" s="47">
         <v>33</v>
       </c>
@@ -5159,7 +5166,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="47">
         <v>35</v>
       </c>
@@ -5180,7 +5187,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="47">
         <v>36</v>
       </c>
@@ -5201,7 +5208,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="47">
         <v>37</v>
       </c>
@@ -5224,7 +5231,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="20">
         <v>38</v>
       </c>
@@ -5326,7 +5333,12 @@
       <c r="G54" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:G42" xr:uid="{478D8F30-1DEF-4E7C-A5F2-B34E61C5B8D1}">
+  <autoFilter ref="A6:G44" xr:uid="{478D8F30-1DEF-4E7C-A5F2-B34E61C5B8D1}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="7-1"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:G9">
       <sortCondition ref="B6"/>
     </sortState>
@@ -6266,14 +6278,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="35fd97c1-9d0a-41c4-8970-db51394a77c9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8deb9ff1-9346-46f5-b365-70a89aa0c9b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6466,21 +6476,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="35fd97c1-9d0a-41c4-8970-db51394a77c9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8deb9ff1-9346-46f5-b365-70a89aa0c9b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DEBACA3-E194-4EA5-9FD2-2B0D013D5013}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE8FF85-9F12-46BD-BFFC-806FCD25A000}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="35fd97c1-9d0a-41c4-8970-db51394a77c9"/>
-    <ds:schemaRef ds:uri="8deb9ff1-9346-46f5-b365-70a89aa0c9b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6505,9 +6514,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE8FF85-9F12-46BD-BFFC-806FCD25A000}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DEBACA3-E194-4EA5-9FD2-2B0D013D5013}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="35fd97c1-9d0a-41c4-8970-db51394a77c9"/>
+    <ds:schemaRef ds:uri="8deb9ff1-9346-46f5-b365-70a89aa0c9b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>